--- a/server/entry/lib/template_schools_shinjin.xlsx
+++ b/server/entry/lib/template_schools_shinjin.xlsx
@@ -2109,7 +2109,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BD82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
@@ -6561,7 +6561,7 @@
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7874015748031497" right="0.7874015748031497" top="0.7874015748031497" bottom="0.3937007874015748" header="0" footer="0.3937007874015748"/>
-  <pageSetup orientation="portrait" paperSize="8" scale="98"/>
+  <pageSetup orientation="portrait" paperSize="8" fitToWidth="1" fitToHeight="1"/>
   <headerFooter alignWithMargins="0">
     <oddHeader/>
     <oddFooter>&amp;L_x000a_&amp;R_x000a_</oddFooter>
@@ -6570,8 +6570,5 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <rowBreaks count="1" manualBreakCount="1">
-    <brk id="78" min="0" max="45" man="1"/>
-  </rowBreaks>
 </worksheet>
 </file>